--- a/Results_greedy.xlsx
+++ b/Results_greedy.xlsx
@@ -471,7 +471,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -521,7 +521,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>17.2</v>
@@ -562,7 +562,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>O3 -&gt; O2</t>
+          <t>O1</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>O1</t>
+          <t>O3 -&gt; O2</t>
         </is>
       </c>
     </row>

--- a/Results_greedy.xlsx
+++ b/Results_greedy.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Resultaten orders" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Volgorde machines" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Schedule" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Totale resulaten" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O3</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -477,20 +477,20 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O1</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -502,32 +502,657 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ORD12</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>25.2</v>
+      <c r="F5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24.67</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ORD11</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>55</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="G6" t="n">
+        <v>26.11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ORD02</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ORD06</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D8" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="G8" t="n">
+        <v>35.33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ORD09</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>109.67</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="G9" t="n">
+        <v>47.67</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ORD07</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ORD05</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="G11" t="n">
+        <v>50.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ORD08</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" t="n">
+        <v>195</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ORD10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>153.33</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="G13" t="n">
+        <v>58.33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ORD14</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="C14" t="n">
+        <v>14</v>
+      </c>
+      <c r="D14" t="n">
+        <v>184.33</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="G14" t="n">
+        <v>61.17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ORD13</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>55</v>
+      </c>
+      <c r="G15" t="n">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ORD25</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>17</v>
+      </c>
+      <c r="C16" t="n">
+        <v>14</v>
+      </c>
+      <c r="D16" t="n">
+        <v>238</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="G16" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ORD16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>68</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ORD15</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>62.17</v>
+      </c>
+      <c r="G18" t="n">
+        <v>72.17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ORD21</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>76</v>
+      </c>
+      <c r="G19" t="n">
+        <v>85.44</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ORD20</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" t="n">
+        <v>228</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ORD19</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>76.17</v>
+      </c>
+      <c r="G21" t="n">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ORD18</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>101.25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ORD27</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="C23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>144.89</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>89.44</v>
+      </c>
+      <c r="G23" t="n">
+        <v>96.11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ORD26</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" t="n">
+        <v>11</v>
+      </c>
+      <c r="D24" t="n">
+        <v>209</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>89</v>
+      </c>
+      <c r="G24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ORD28</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>30.89</v>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>185.33</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>100.11</v>
+      </c>
+      <c r="G25" t="n">
+        <v>112.89</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ORD17</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>22</v>
+      </c>
+      <c r="C26" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" t="n">
+        <v>264</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ORD22</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>256.67</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>111.67</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ORD23</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>23</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>207</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>118</v>
+      </c>
+      <c r="G28" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ORD24</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="C29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" t="n">
+        <v>151</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>117.67</v>
+      </c>
+      <c r="G29" t="n">
+        <v>125.58</v>
       </c>
     </row>
   </sheetData>
@@ -541,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,7 +1187,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>O1</t>
+          <t>ORD04 -&gt; ORD02 -&gt; ORD07 -&gt; ORD08 -&gt; ORD13 -&gt; ORD16 -&gt; ORD20 -&gt; ORD26 -&gt; ORD17 -&gt; ORD23</t>
         </is>
       </c>
     </row>
@@ -572,7 +1197,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>O3 -&gt; O2</t>
+          <t>ORD03 -&gt; ORD12 -&gt; ORD06 -&gt; ORD05 -&gt; ORD14 -&gt; ORD15 -&gt; ORD19 -&gt; ORD18 -&gt; ORD22 -&gt; ORD24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ORD01 -&gt; ORD11 -&gt; ORD09 -&gt; ORD10 -&gt; ORD25 -&gt; ORD21 -&gt; ORD27 -&gt; ORD28</t>
         </is>
       </c>
     </row>
@@ -609,7 +1244,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>357.6389</v>
       </c>
     </row>
     <row r="3">
@@ -619,7 +1254,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>3597.75</v>
       </c>
     </row>
   </sheetData>

--- a/Results_greedy.xlsx
+++ b/Results_greedy.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resultaten orders" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Totale resulaten" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Schedule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Totale resultaten" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,32 +425,52 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>tardiness</t>
+          <t>Machine</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>SeqNo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Tardiness</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Penalty</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Tot_penalty</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Machine</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>begintijd</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>eindtijd</t>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Cost</t>
         </is>
       </c>
     </row>
@@ -461,24 +480,38 @@
           <t>ORD03</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G2" t="n">
         <v>7.5</v>
       </c>
+      <c r="H2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,24 +519,38 @@
           <t>ORD04</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G3" t="n">
         <v>8.5</v>
       </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -511,24 +558,38 @@
           <t>ORD01</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="G4" t="n">
         <v>8.33</v>
       </c>
+      <c r="H4" t="n">
+        <v>17</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -536,24 +597,38 @@
           <t>ORD12</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>6.67</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>15.5</v>
       </c>
       <c r="F5" t="n">
-        <v>15.5</v>
+        <v>9.17</v>
       </c>
       <c r="G5" t="n">
         <v>24.67</v>
       </c>
+      <c r="H5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -561,24 +636,38 @@
           <t>ORD11</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>6.11</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>13.33</v>
       </c>
       <c r="F6" t="n">
-        <v>13.33</v>
+        <v>12.78</v>
       </c>
       <c r="G6" t="n">
         <v>26.11</v>
       </c>
+      <c r="H6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -586,24 +675,38 @@
           <t>ORD02</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.5</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>18.5</v>
       </c>
       <c r="F7" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
         <v>28.5</v>
       </c>
+      <c r="H7" t="n">
+        <v>28</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -611,24 +714,38 @@
           <t>ORD06</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>4.33</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>47.67</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>28.67</v>
       </c>
       <c r="F8" t="n">
-        <v>28.67</v>
+        <v>6.67</v>
       </c>
       <c r="G8" t="n">
         <v>35.33</v>
       </c>
+      <c r="H8" t="n">
+        <v>31</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11</v>
+      </c>
+      <c r="K8" t="n">
+        <v>47.67</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -636,24 +753,38 @@
           <t>ORD09</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>15.67</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>109.67</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>37.11</v>
       </c>
       <c r="F9" t="n">
-        <v>37.11</v>
+        <v>10.56</v>
       </c>
       <c r="G9" t="n">
         <v>47.67</v>
       </c>
+      <c r="H9" t="n">
+        <v>32</v>
+      </c>
+      <c r="I9" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>109.67</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -661,24 +792,38 @@
           <t>ORD07</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>2.5</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>30.5</v>
       </c>
       <c r="F10" t="n">
-        <v>30.5</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
         <v>37.5</v>
       </c>
+      <c r="H10" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14</v>
+      </c>
+      <c r="K10" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -686,24 +831,38 @@
           <t>ORD05</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>14.75</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>132.75</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>45.33</v>
       </c>
       <c r="F11" t="n">
-        <v>45.33</v>
+        <v>5.42</v>
       </c>
       <c r="G11" t="n">
         <v>50.75</v>
       </c>
+      <c r="H11" t="n">
+        <v>36</v>
+      </c>
+      <c r="I11" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>132.75</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -711,24 +870,38 @@
           <t>ORD08</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>15</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>195</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>42.5</v>
       </c>
       <c r="F12" t="n">
-        <v>42.5</v>
+        <v>10.5</v>
       </c>
       <c r="G12" t="n">
         <v>53</v>
       </c>
+      <c r="H12" t="n">
+        <v>38</v>
+      </c>
+      <c r="I12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -736,24 +909,38 @@
           <t>ORD10</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>15.33</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>153.33</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>51.67</v>
       </c>
       <c r="F13" t="n">
-        <v>51.67</v>
+        <v>6.67</v>
       </c>
       <c r="G13" t="n">
         <v>58.33</v>
       </c>
+      <c r="H13" t="n">
+        <v>43</v>
+      </c>
+      <c r="I13" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" t="n">
+        <v>153.33</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -761,24 +948,38 @@
           <t>ORD14</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>13.17</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>184.33</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>50.75</v>
       </c>
       <c r="F14" t="n">
-        <v>50.75</v>
+        <v>10.42</v>
       </c>
       <c r="G14" t="n">
         <v>61.17</v>
       </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="J14" t="n">
+        <v>14</v>
+      </c>
+      <c r="K14" t="n">
+        <v>184.33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -786,24 +987,38 @@
           <t>ORD13</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>11.5</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>126.5</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>5.5</v>
       </c>
       <c r="G15" t="n">
         <v>60.5</v>
       </c>
+      <c r="H15" t="n">
+        <v>49</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K15" t="n">
+        <v>126.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -811,24 +1026,38 @@
           <t>ORD25</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>17</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>58.33</v>
       </c>
       <c r="F16" t="n">
-        <v>58.33</v>
+        <v>11.67</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
       </c>
+      <c r="H16" t="n">
+        <v>53</v>
+      </c>
+      <c r="I16" t="n">
+        <v>17</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>238</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -836,24 +1065,38 @@
           <t>ORD16</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>8.5</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
       </c>
       <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F17" t="n">
         <v>8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>68</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>63.5</v>
       </c>
       <c r="G17" t="n">
         <v>71.5</v>
       </c>
+      <c r="H17" t="n">
+        <v>63</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -861,24 +1104,38 @@
           <t>ORD15</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>6.17</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>55.5</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>62.17</v>
       </c>
       <c r="F18" t="n">
-        <v>62.17</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
         <v>72.17</v>
       </c>
+      <c r="H18" t="n">
+        <v>66</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>55.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -886,24 +1143,38 @@
           <t>ORD21</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>16.44</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>115.11</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="F19" t="n">
-        <v>76</v>
+        <v>9.44</v>
       </c>
       <c r="G19" t="n">
         <v>85.44</v>
       </c>
+      <c r="H19" t="n">
+        <v>69</v>
+      </c>
+      <c r="I19" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>115.11</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -911,24 +1182,38 @@
           <t>ORD20</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>19</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>228</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>81.5</v>
       </c>
       <c r="F20" t="n">
-        <v>81.5</v>
+        <v>7.5</v>
       </c>
       <c r="G20" t="n">
         <v>89</v>
       </c>
+      <c r="H20" t="n">
+        <v>70</v>
+      </c>
+      <c r="I20" t="n">
+        <v>19</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12</v>
+      </c>
+      <c r="K20" t="n">
+        <v>228</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -936,24 +1221,38 @@
           <t>ORD19</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>10.5</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>157.5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>76.17</v>
       </c>
       <c r="F21" t="n">
-        <v>76.17</v>
+        <v>8.33</v>
       </c>
       <c r="G21" t="n">
         <v>84.5</v>
       </c>
+      <c r="H21" t="n">
+        <v>74</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>15</v>
+      </c>
+      <c r="K21" t="n">
+        <v>157.5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -961,24 +1260,38 @@
           <t>ORD18</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>23.25</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>232.5</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>92.5</v>
       </c>
       <c r="F22" t="n">
-        <v>92.5</v>
+        <v>8.75</v>
       </c>
       <c r="G22" t="n">
         <v>101.25</v>
       </c>
+      <c r="H22" t="n">
+        <v>78</v>
+      </c>
+      <c r="I22" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>10</v>
+      </c>
+      <c r="K22" t="n">
+        <v>232.5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -986,24 +1299,38 @@
           <t>ORD27</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>18.11</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>144.89</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>89.44</v>
       </c>
       <c r="F23" t="n">
-        <v>89.44</v>
+        <v>6.67</v>
       </c>
       <c r="G23" t="n">
         <v>96.11</v>
       </c>
+      <c r="H23" t="n">
+        <v>78</v>
+      </c>
+      <c r="I23" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>144.89</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1011,24 +1338,38 @@
           <t>ORD26</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>19</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
       </c>
       <c r="C24" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>89</v>
+      </c>
+      <c r="F24" t="n">
         <v>11</v>
-      </c>
-      <c r="D24" t="n">
-        <v>209</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>89</v>
       </c>
       <c r="G24" t="n">
         <v>100</v>
       </c>
+      <c r="H24" t="n">
+        <v>81</v>
+      </c>
+      <c r="I24" t="n">
+        <v>19</v>
+      </c>
+      <c r="J24" t="n">
+        <v>11</v>
+      </c>
+      <c r="K24" t="n">
+        <v>209</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1036,24 +1377,38 @@
           <t>ORD28</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>30.89</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>185.33</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>100.11</v>
       </c>
       <c r="F25" t="n">
-        <v>100.11</v>
+        <v>12.78</v>
       </c>
       <c r="G25" t="n">
         <v>112.89</v>
       </c>
+      <c r="H25" t="n">
+        <v>82</v>
+      </c>
+      <c r="I25" t="n">
+        <v>30.89</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>185.33</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1061,24 +1416,38 @@
           <t>ORD17</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>22</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
         <v>107</v>
       </c>
+      <c r="H26" t="n">
+        <v>85</v>
+      </c>
+      <c r="I26" t="n">
+        <v>22</v>
+      </c>
+      <c r="J26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" t="n">
+        <v>264</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1086,24 +1455,38 @@
           <t>ORD22</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>25.67</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>256.67</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>106.25</v>
       </c>
       <c r="F27" t="n">
-        <v>106.25</v>
+        <v>5.42</v>
       </c>
       <c r="G27" t="n">
         <v>111.67</v>
       </c>
+      <c r="H27" t="n">
+        <v>86</v>
+      </c>
+      <c r="I27" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="J27" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" t="n">
+        <v>256.67</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1111,24 +1494,38 @@
           <t>ORD23</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>23</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
       </c>
       <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" t="n">
+        <v>118</v>
+      </c>
+      <c r="F28" t="n">
         <v>9</v>
-      </c>
-      <c r="D28" t="n">
-        <v>207</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>118</v>
       </c>
       <c r="G28" t="n">
         <v>127</v>
       </c>
+      <c r="H28" t="n">
+        <v>104</v>
+      </c>
+      <c r="I28" t="n">
+        <v>23</v>
+      </c>
+      <c r="J28" t="n">
+        <v>9</v>
+      </c>
+      <c r="K28" t="n">
+        <v>207</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1136,23 +1533,37 @@
           <t>ORD24</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>12.58</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>151</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>117.67</v>
       </c>
       <c r="F29" t="n">
-        <v>117.67</v>
+        <v>7.92</v>
       </c>
       <c r="G29" t="n">
         <v>125.58</v>
+      </c>
+      <c r="H29" t="n">
+        <v>113</v>
+      </c>
+      <c r="I29" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="J29" t="n">
+        <v>12</v>
+      </c>
+      <c r="K29" t="n">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1166,62 +1577,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Machine_number</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Order machine</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ORD04 -&gt; ORD02 -&gt; ORD07 -&gt; ORD08 -&gt; ORD13 -&gt; ORD16 -&gt; ORD20 -&gt; ORD26 -&gt; ORD17 -&gt; ORD23</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ORD03 -&gt; ORD12 -&gt; ORD06 -&gt; ORD05 -&gt; ORD14 -&gt; ORD15 -&gt; ORD19 -&gt; ORD18 -&gt; ORD22 -&gt; ORD24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ORD01 -&gt; ORD11 -&gt; ORD09 -&gt; ORD10 -&gt; ORD25 -&gt; ORD21 -&gt; ORD27 -&gt; ORD28</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
